--- a/ASML.xlsx
+++ b/ASML.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF5595CB-C9CE-429C-9590-B4EBC32D40D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3073AB92-6A9E-4064-861A-7F151D6A7267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11250" yWindow="4360" windowWidth="26500" windowHeight="15380" activeTab="1" xr2:uid="{0CB1B3B1-96D5-464B-8AAB-50F0DEF28373}"/>
+    <workbookView xWindow="17610" yWindow="6820" windowWidth="19890" windowHeight="10280" activeTab="1" xr2:uid="{0CB1B3B1-96D5-464B-8AAB-50F0DEF28373}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
   <si>
     <t>Price</t>
   </si>
@@ -121,6 +121,36 @@
   </si>
   <si>
     <t>Operating Income</t>
+  </si>
+  <si>
+    <t>Q125</t>
+  </si>
+  <si>
+    <t>Q225</t>
+  </si>
+  <si>
+    <t>Q325</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Service</t>
   </si>
 </sst>
 </file>
@@ -149,12 +179,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -169,7 +205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -182,6 +218,9 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -593,22 +632,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6E5B56-48A6-214D-919A-AB73CF1B0447}">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="10" width="7.58203125" style="4" customWidth="1"/>
-    <col min="11" max="14" width="7.08203125" style="4" customWidth="1"/>
-    <col min="15" max="16384" width="10.6640625" style="1"/>
+    <col min="11" max="22" width="7.08203125" style="4" customWidth="1"/>
+    <col min="23" max="16384" width="10.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
@@ -645,8 +684,32 @@
       <c r="N2" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>20</v>
       </c>
@@ -666,7 +729,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
@@ -686,101 +749,168 @@
         <v>5567</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="B6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7">
-        <v>6902</v>
-      </c>
-      <c r="I6" s="7">
-        <v>6673</v>
-      </c>
-      <c r="J6" s="7">
-        <v>7237</v>
-      </c>
-      <c r="K6" s="7">
-        <v>5290</v>
-      </c>
-      <c r="L6" s="7">
-        <v>6243</v>
-      </c>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-    </row>
-    <row r="7" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="5">
-        <v>3358.3</v>
-      </c>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5">
-        <v>3030.6</v>
-      </c>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-    </row>
-    <row r="8" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H7" s="5"/>
+      <c r="I7" s="5">
+        <v>5308.2</v>
+      </c>
+      <c r="J7" s="5">
+        <v>5926</v>
+      </c>
+      <c r="K7" s="8">
+        <v>3965.9</v>
+      </c>
+      <c r="L7" s="8">
+        <v>4760.8999999999996</v>
+      </c>
+      <c r="M7" s="8">
+        <v>5926</v>
+      </c>
+      <c r="N7" s="8">
+        <v>7115.9</v>
+      </c>
+      <c r="O7" s="8">
+        <v>5740.4</v>
+      </c>
+      <c r="P7" s="8">
+        <v>5596.1</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>5553.8</v>
+      </c>
+      <c r="R7" s="8">
+        <v>7584</v>
+      </c>
+      <c r="S7" s="8">
+        <v>6279.4</v>
+      </c>
+      <c r="T7" s="8">
+        <v>6564.8</v>
+      </c>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+    </row>
+    <row r="8" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="5">
-        <f>H6-H7</f>
-        <v>3543.7</v>
-      </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5">
-        <f>L6-L7</f>
-        <v>3212.4</v>
-      </c>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-    </row>
-    <row r="9" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5">
-        <v>999.9</v>
-      </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5">
-        <v>1100.5999999999999</v>
-      </c>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-    </row>
-    <row r="10" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H8" s="5"/>
+      <c r="I8" s="5">
+        <v>1364.8</v>
+      </c>
+      <c r="J8" s="5">
+        <v>1541.3</v>
+      </c>
+      <c r="K8" s="8">
+        <v>1324.1</v>
+      </c>
+      <c r="L8" s="8">
+        <v>1481.9</v>
+      </c>
+      <c r="M8" s="8">
+        <v>1541.3</v>
+      </c>
+      <c r="N8" s="8">
+        <v>2146.9</v>
+      </c>
+      <c r="O8" s="8">
+        <v>2001.1</v>
+      </c>
+      <c r="P8" s="8">
+        <v>2095.6</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>1962.2</v>
+      </c>
+      <c r="R8" s="8">
+        <v>2134.1</v>
+      </c>
+      <c r="S8" s="8">
+        <v>2487.5</v>
+      </c>
+      <c r="T8" s="8">
+        <v>2761.7</v>
+      </c>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+    </row>
+    <row r="9" spans="1:22" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7">
+        <v>6902</v>
+      </c>
+      <c r="I9" s="7">
+        <v>6673</v>
+      </c>
+      <c r="J9" s="7">
+        <v>7237</v>
+      </c>
+      <c r="K9" s="7">
+        <f t="shared" ref="J9:S9" si="0">+K7+K8</f>
+        <v>5290</v>
+      </c>
+      <c r="L9" s="7">
+        <f t="shared" si="0"/>
+        <v>6242.7999999999993</v>
+      </c>
+      <c r="M9" s="7">
+        <f t="shared" si="0"/>
+        <v>7467.3</v>
+      </c>
+      <c r="N9" s="7">
+        <f t="shared" si="0"/>
+        <v>9262.7999999999993</v>
+      </c>
+      <c r="O9" s="7">
+        <f t="shared" si="0"/>
+        <v>7741.5</v>
+      </c>
+      <c r="P9" s="7">
+        <f t="shared" si="0"/>
+        <v>7691.7000000000007</v>
+      </c>
+      <c r="Q9" s="7">
+        <f t="shared" si="0"/>
+        <v>7516</v>
+      </c>
+      <c r="R9" s="7">
+        <f t="shared" si="0"/>
+        <v>9718.1</v>
+      </c>
+      <c r="S9" s="7">
+        <f t="shared" si="0"/>
+        <v>8766.9</v>
+      </c>
+      <c r="T9" s="7">
+        <f>+T7+T8</f>
+        <v>9326.5</v>
+      </c>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+    </row>
+    <row r="10" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -788,20 +918,30 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5">
-        <v>281.10000000000002</v>
+        <v>3358.3</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5">
-        <v>277</v>
+        <v>3030.6</v>
       </c>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
-    </row>
-    <row r="11" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5">
+        <v>4291.1000000000004</v>
+      </c>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+    </row>
+    <row r="11" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -809,31 +949,33 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5">
-        <f>H10+H9</f>
-        <v>1281</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" ref="I11:L11" si="0">I10+I9</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+        <f>H9-H10</f>
+        <v>3543.7</v>
+      </c>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
       <c r="L11" s="5">
-        <f t="shared" si="0"/>
-        <v>1377.6</v>
+        <f>L9-L10</f>
+        <v>3212.1999999999994</v>
       </c>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
-    </row>
-    <row r="12" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5">
+        <f>+T9-T10</f>
+        <v>5035.3999999999996</v>
+      </c>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+    </row>
+    <row r="12" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -841,49 +983,207 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5">
-        <f>H8-H11</f>
-        <v>2262.6999999999998</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" ref="I12:L12" si="1">I8-I11</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+        <v>999.9</v>
+      </c>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
       <c r="L12" s="5">
-        <f t="shared" si="1"/>
-        <v>1834.8000000000002</v>
+        <v>1100.5999999999999</v>
       </c>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="L13" s="4">
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+    </row>
+    <row r="13" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5">
+        <v>281.10000000000002</v>
+      </c>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5">
+        <v>277</v>
+      </c>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+    </row>
+    <row r="14" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5">
+        <f>H13+H12</f>
+        <v>1281</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" ref="I14:L14" si="1">I13+I12</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="1"/>
+        <v>1377.6</v>
+      </c>
+      <c r="M14" s="5">
+        <f t="shared" ref="M14:T14" si="2">M13+M12</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+    </row>
+    <row r="15" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5">
+        <f>H11-H14</f>
+        <v>2262.6999999999998</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" ref="I15:L15" si="3">I11-I14</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <f t="shared" si="3"/>
+        <v>1834.5999999999995</v>
+      </c>
+      <c r="M15" s="5">
+        <f t="shared" ref="M15:T15" si="4">M11-M14</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O15" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P15" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="R15" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="5">
+        <f t="shared" si="4"/>
+        <v>5035.3999999999996</v>
+      </c>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="L16" s="4">
         <v>-11.9</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="L14" s="5">
-        <f>L12+L13</f>
-        <v>1822.9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="L15" s="4">
+    <row r="17" spans="12:20" x14ac:dyDescent="0.25">
+      <c r="L17" s="5">
+        <f>L15+L16</f>
+        <v>1822.6999999999994</v>
+      </c>
+      <c r="P17" s="5"/>
+      <c r="T17" s="5"/>
+    </row>
+    <row r="18" spans="12:20" x14ac:dyDescent="0.25">
+      <c r="L18" s="4">
         <v>291.60000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="L16" s="5">
-        <f>L14-L15</f>
-        <v>1531.3000000000002</v>
-      </c>
+    <row r="19" spans="12:20" x14ac:dyDescent="0.25">
+      <c r="L19" s="5">
+        <f>L17-L18</f>
+        <v>1531.0999999999995</v>
+      </c>
+      <c r="P19" s="5"/>
+      <c r="T19" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
